--- a/data-raw/arbol_estadistico.xlsx
+++ b/data-raw/arbol_estadistico.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">script_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Estadística Descriptiva</t>
+    <t xml:space="preserve">Descriptive statistics</t>
   </si>
   <si>
     <t xml:space="preserve">1 Var</t>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">s005</t>
   </si>
   <si>
-    <t xml:space="preserve">Pruebas de hipotesis clasicas</t>
+    <t xml:space="preserve">Classical hypothesis testing</t>
   </si>
   <si>
     <t xml:space="preserve">Test de Uniformidad</t>
@@ -190,7 +190,7 @@
     <t xml:space="preserve">s019</t>
   </si>
   <si>
-    <t xml:space="preserve">Modelos Lineales</t>
+    <t xml:space="preserve">General Linear Models</t>
   </si>
   <si>
     <t xml:space="preserve">Fijos</t>
@@ -337,7 +337,7 @@
     <t xml:space="preserve">s041</t>
   </si>
   <si>
-    <t xml:space="preserve">Modelos Lineales Generalizados</t>
+    <t xml:space="preserve">Generalized Linear Models</t>
   </si>
   <si>
     <t xml:space="preserve">Binomial</t>
@@ -418,12 +418,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF860D"/>
+        <bgColor rgb="FFFF8000"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -434,7 +440,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8000"/>
-        <bgColor rgb="FFFF6600"/>
+        <bgColor rgb="FFFF860D"/>
       </patternFill>
     </fill>
     <fill>
@@ -446,7 +452,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
-        <bgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF860D"/>
       </patternFill>
     </fill>
     <fill>
@@ -490,7 +496,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -503,8 +509,16 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -520,6 +534,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -578,8 +596,8 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFBF00"/>
+      <rgbColor rgb="FFFF860D"/>
       <rgbColor rgb="FFFF8000"/>
-      <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
@@ -778,11 +796,12 @@
   <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="26.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.29"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -808,1028 +827,1028 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="4" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" s="4" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" s="4" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" s="4" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" s="4" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="F8" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="F9" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="F10" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="11" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="F11" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="12" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="F12" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+    <row r="13" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="F13" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="14" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="F14" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    <row r="15" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="F15" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+    <row r="16" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="F16" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="F17" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+    <row r="18" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="F18" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+    <row r="19" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="F19" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+    <row r="20" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="F20" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="4" t="s">
+    <row r="21" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="F21" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="4" t="s">
+    <row r="22" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="F22" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="4" t="s">
+    <row r="23" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="F23" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="4" t="s">
+    <row r="24" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="F24" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="25" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="4" t="s">
+    <row r="25" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="F25" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="4" t="s">
+    <row r="26" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="F26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F27" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="F27" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="28" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B28" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="F28" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="B29" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="F29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="6" t="s">
+    <row r="30" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F30" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G30" s="3" t="s">
+      <c r="F30" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="31" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="6" t="s">
+    <row r="31" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G31" s="3" t="s">
+      <c r="F31" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="32" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="6" t="s">
+    <row r="32" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F32" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G32" s="3" t="s">
+      <c r="F32" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="7" t="s">
+    <row r="33" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G33" s="3" t="s">
+      <c r="F33" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G33" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="34" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="7" t="s">
+    <row r="34" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="F34" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="35" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="7" t="s">
+    <row r="35" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G35" s="3" t="s">
+      <c r="F35" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G35" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="36" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="7" t="s">
+    <row r="36" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G36" s="3" t="s">
+      <c r="F36" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="37" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="7" t="s">
+    <row r="37" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G37" s="3" t="s">
+      <c r="F37" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="38" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="7" t="s">
+    <row r="38" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F38" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G38" s="3" t="s">
+      <c r="F38" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="39" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="7" t="s">
+    <row r="39" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F39" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G39" s="3" t="s">
+      <c r="F39" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G39" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="4" t="s">
+    <row r="40" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F40" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G40" s="3" t="s">
+      <c r="F40" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="41" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="4" t="s">
+    <row r="41" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G41" s="3" t="s">
+      <c r="F41" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="42" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="3" t="s">
+    <row r="42" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G42" s="3" t="s">
+      <c r="F42" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="4" t="s">
+      <c r="B43" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="7" t="s">
         <v>59</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G43" s="3" t="s">
+      <c r="F43" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C44" s="4" t="s">
+      <c r="B44" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="7" t="s">
         <v>59</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G44" s="3" t="s">
+      <c r="F44" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C45" s="4" t="s">
+      <c r="B45" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="7" t="s">
         <v>59</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G45" s="3" t="s">
+      <c r="F45" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" s="4" t="s">
+      <c r="B46" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="7" t="s">
         <v>59</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G46" s="3" t="s">
+      <c r="F46" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C47" s="4" t="s">
+      <c r="B47" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="10" t="s">
         <v>85</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G47" s="3" t="s">
+      <c r="F47" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G47" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="4" t="s">
+      <c r="B48" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="10" t="s">
         <v>85</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G48" s="3" t="s">
+      <c r="F48" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="4" t="s">
+      <c r="B49" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="10" t="s">
         <v>85</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G49" s="3" t="s">
+      <c r="F49" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G49" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+    <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" s="4" t="s">
+      <c r="B50" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="10" t="s">
         <v>85</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="G50" s="3" t="s">
+      <c r="F50" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>118</v>
       </c>
     </row>

--- a/data-raw/arbol_estadistico.xlsx
+++ b/data-raw/arbol_estadistico.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="120">
   <si>
     <t xml:space="preserve">Nivel1</t>
   </si>
@@ -190,10 +190,16 @@
     <t xml:space="preserve">s019</t>
   </si>
   <si>
+    <t xml:space="preserve">Test t para dos muestras apareadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s020</t>
+  </si>
+  <si>
     <t xml:space="preserve">General Linear Models</t>
   </si>
   <si>
-    <t xml:space="preserve">Fijos</t>
+    <t xml:space="preserve">Fixed effects</t>
   </si>
   <si>
     <t xml:space="preserve">Anova</t>
@@ -202,37 +208,37 @@
     <t xml:space="preserve">Anova 1 Way</t>
   </si>
   <si>
-    <t xml:space="preserve">s020</t>
+    <t xml:space="preserve">s021</t>
   </si>
   <si>
     <t xml:space="preserve">Anova 1 Way + Contrasts</t>
   </si>
   <si>
-    <t xml:space="preserve">s021</t>
+    <t xml:space="preserve">s022</t>
   </si>
   <si>
     <t xml:space="preserve">Anova 1 Way + 1 Block</t>
   </si>
   <si>
-    <t xml:space="preserve">s022</t>
+    <t xml:space="preserve">s023</t>
   </si>
   <si>
     <t xml:space="preserve">Anova 2 Ways</t>
   </si>
   <si>
-    <t xml:space="preserve">s023</t>
+    <t xml:space="preserve">s024</t>
   </si>
   <si>
     <t xml:space="preserve">Anova 3 Ways</t>
   </si>
   <si>
-    <t xml:space="preserve">s024</t>
+    <t xml:space="preserve">s025</t>
   </si>
   <si>
     <t xml:space="preserve">Anova Multi Ways</t>
   </si>
   <si>
-    <t xml:space="preserve">s025</t>
+    <t xml:space="preserve">s026</t>
   </si>
   <si>
     <t xml:space="preserve">Ancova</t>
@@ -241,19 +247,19 @@
     <t xml:space="preserve">Ancova (with interaction)</t>
   </si>
   <si>
-    <t xml:space="preserve">s026</t>
+    <t xml:space="preserve">s027</t>
   </si>
   <si>
     <t xml:space="preserve">Ancova (without interaction)</t>
   </si>
   <si>
-    <t xml:space="preserve">s027</t>
+    <t xml:space="preserve">s028</t>
   </si>
   <si>
     <t xml:space="preserve">Ancova (with and without interaction)</t>
   </si>
   <si>
-    <t xml:space="preserve">s028</t>
+    <t xml:space="preserve">s029</t>
   </si>
   <si>
     <t xml:space="preserve">Dummy</t>
@@ -262,111 +268,105 @@
     <t xml:space="preserve">Dummy (with interaction)</t>
   </si>
   <si>
-    <t xml:space="preserve">s029</t>
+    <t xml:space="preserve">s030</t>
   </si>
   <si>
     <t xml:space="preserve">Dummy (without interaction)</t>
   </si>
   <si>
-    <t xml:space="preserve">s030</t>
-  </si>
-  <si>
     <t xml:space="preserve">s031</t>
   </si>
   <si>
-    <t xml:space="preserve">Regresión Lineal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lineal Simple</t>
-  </si>
-  <si>
     <t xml:space="preserve">s032</t>
   </si>
   <si>
-    <t xml:space="preserve">Lineal Doble</t>
+    <t xml:space="preserve">Linear regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple linear regression</t>
   </si>
   <si>
     <t xml:space="preserve">s033</t>
   </si>
   <si>
-    <t xml:space="preserve">Lineal Multi</t>
+    <t xml:space="preserve">Double linear regression</t>
   </si>
   <si>
     <t xml:space="preserve">s034</t>
   </si>
   <si>
+    <t xml:space="preserve">Multiple linear regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s035</t>
+  </si>
+  <si>
     <t xml:space="preserve">Model Selection – Foreward</t>
   </si>
   <si>
-    <t xml:space="preserve">s035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model Selection – backward</t>
-  </si>
-  <si>
     <t xml:space="preserve">s036</t>
   </si>
   <si>
+    <t xml:space="preserve">Model Selection – Backward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s037</t>
+  </si>
+  <si>
     <t xml:space="preserve">Model Selection – Foreward y backward</t>
   </si>
   <si>
-    <t xml:space="preserve">s037</t>
+    <t xml:space="preserve">s038</t>
   </si>
   <si>
     <t xml:space="preserve">Model Selection – All Models</t>
   </si>
   <si>
-    <t xml:space="preserve">s038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aleatorios</t>
-  </si>
-  <si>
     <t xml:space="preserve">s039</t>
   </si>
   <si>
+    <t xml:space="preserve">Random effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s040</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anova 2 Way</t>
   </si>
   <si>
-    <t xml:space="preserve">s040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixtos</t>
-  </si>
-  <si>
     <t xml:space="preserve">s041</t>
   </si>
   <si>
+    <t xml:space="preserve">Mixed effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s042</t>
+  </si>
+  <si>
     <t xml:space="preserve">Generalized Linear Models</t>
   </si>
   <si>
     <t xml:space="preserve">Binomial</t>
   </si>
   <si>
-    <t xml:space="preserve">s042</t>
+    <t xml:space="preserve">s043</t>
   </si>
   <si>
     <t xml:space="preserve">Poisson</t>
   </si>
   <si>
-    <t xml:space="preserve">s043</t>
+    <t xml:space="preserve">s044</t>
   </si>
   <si>
     <t xml:space="preserve">Gamma</t>
   </si>
   <si>
-    <t xml:space="preserve">s044</t>
+    <t xml:space="preserve">s045</t>
   </si>
   <si>
     <t xml:space="preserve">Gausiana</t>
   </si>
   <si>
-    <t xml:space="preserve">s045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regresion Lineal</t>
-  </si>
-  <si>
     <t xml:space="preserve">s046</t>
   </si>
   <si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t xml:space="preserve">s049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s050</t>
   </si>
 </sst>
 </file>
@@ -496,7 +499,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -535,6 +538,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -798,7 +805,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="26.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.29"/>
@@ -912,7 +919,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
@@ -928,11 +935,11 @@
       <c r="F7" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
@@ -948,11 +955,11 @@
       <c r="F8" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -971,11 +978,11 @@
       <c r="F9" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
@@ -994,11 +1001,11 @@
       <c r="F10" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -1017,11 +1024,11 @@
       <c r="F11" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
@@ -1040,11 +1047,11 @@
       <c r="F12" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
@@ -1063,11 +1070,11 @@
       <c r="F13" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -1086,11 +1093,11 @@
       <c r="F14" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
@@ -1109,11 +1116,11 @@
       <c r="F15" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
@@ -1132,11 +1139,11 @@
       <c r="F16" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -1155,11 +1162,11 @@
       <c r="F17" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
@@ -1178,11 +1185,11 @@
       <c r="F18" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -1201,11 +1208,11 @@
       <c r="F19" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" s="6" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -1224,39 +1231,42 @@
       <c r="F20" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="F21" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="22" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>61</v>
@@ -1264,19 +1274,19 @@
       <c r="F22" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="23" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>63</v>
@@ -1284,19 +1294,19 @@
       <c r="F23" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="24" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>65</v>
@@ -1304,19 +1314,19 @@
       <c r="F24" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="25" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>67</v>
@@ -1324,19 +1334,19 @@
       <c r="F25" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="26" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>69</v>
@@ -1344,39 +1354,39 @@
       <c r="F26" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="F27" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="28" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>74</v>
@@ -1384,19 +1394,19 @@
       <c r="F28" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>76</v>
@@ -1404,39 +1414,39 @@
       <c r="F29" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="F30" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="31" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>81</v>
@@ -1444,265 +1454,262 @@
       <c r="F31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="32" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="33" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="F33" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="G33" s="6" t="s">
+    </row>
+    <row r="34" s="11" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="34" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="F34" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="35" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="11" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>84</v>
+        <v>58</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="G35" s="6" t="s">
+      <c r="F35" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="36" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" s="11" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>84</v>
+        <v>58</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="F36" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="37" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="G37" s="6" t="s">
+      <c r="F37" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="38" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="F38" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="39" s="10" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="G39" s="6" t="s">
+      <c r="F39" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="F40" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="41" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D41" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F41" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="F42" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="C43" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>57</v>
+        <v>107</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>108</v>
@@ -1710,22 +1717,22 @@
       <c r="F44" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="4" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>57</v>
+        <v>107</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>110</v>
@@ -1733,22 +1740,22 @@
       <c r="F45" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="4" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>57</v>
+        <v>107</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>112</v>
@@ -1756,45 +1763,45 @@
       <c r="F46" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>57</v>
+        <v>107</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C47" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="F47" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>108</v>
@@ -1802,22 +1809,22 @@
       <c r="F48" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>110</v>
@@ -1825,22 +1832,22 @@
       <c r="F49" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G49" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>112</v>
@@ -1848,11 +1855,33 @@
       <c r="F50" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/data-raw/arbol_estadistico.xlsx
+++ b/data-raw/arbol_estadistico.xlsx
@@ -100,7 +100,35 @@
     <t xml:space="preserve">Forma</t>
   </si>
   <si>
-    <t xml:space="preserve">Test de Normalidad Shapiro-Wilks</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Test de Normalidad </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/n </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Shapiro-Wilks</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">s008</t>
@@ -154,7 +182,35 @@
     <t xml:space="preserve">Cuantitativas Independientes</t>
   </si>
   <si>
-    <t xml:space="preserve">Test t para dos muestras independietes</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Test t para dos </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/n </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">muestras independietes</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">s015</t>
@@ -211,7 +267,35 @@
     <t xml:space="preserve">s021</t>
   </si>
   <si>
-    <t xml:space="preserve">Anova 1 Way + Contrasts</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anova 1 Way /n + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/n </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Contrasts</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">s022</t>
@@ -256,7 +340,35 @@
     <t xml:space="preserve">s028</t>
   </si>
   <si>
-    <t xml:space="preserve">Ancova (with and without interaction)</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ancova (with and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/n </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">without interaction)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">s029</t>
@@ -389,7 +501,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,6 +531,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -512,7 +630,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -520,7 +638,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -540,7 +658,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -808,7 +926,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="26.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.29"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/data-raw/arbol_estadistico.xlsx
+++ b/data-raw/arbol_estadistico.xlsx
@@ -100,35 +100,7 @@
     <t xml:space="preserve">Forma</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Test de Normalidad </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/n </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Shapiro-Wilks</t>
-    </r>
+    <t xml:space="preserve">Test de Normalidad /n Shapiro-Wilks</t>
   </si>
   <si>
     <t xml:space="preserve">s008</t>
@@ -182,35 +154,7 @@
     <t xml:space="preserve">Cuantitativas Independientes</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Test t para dos </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/n </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">muestras independietes</t>
-    </r>
+    <t xml:space="preserve">Test t para dos /n muestras independietes</t>
   </si>
   <si>
     <t xml:space="preserve">s015</t>
@@ -264,38 +208,10 @@
     <t xml:space="preserve">Anova 1 Way</t>
   </si>
   <si>
-    <t xml:space="preserve">s021</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Anova 1 Way /n + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/n </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Contrasts</t>
-    </r>
+    <t xml:space="preserve">tool_0001_script_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anova 1 Way /n + /n Contrasts</t>
   </si>
   <si>
     <t xml:space="preserve">s022</t>
@@ -340,35 +256,7 @@
     <t xml:space="preserve">s028</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Ancova (with and </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/n </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">without interaction)</t>
-    </r>
+    <t xml:space="preserve">Ancova (with and /n without interaction)</t>
   </si>
   <si>
     <t xml:space="preserve">s029</t>
@@ -501,7 +389,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,12 +419,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">

--- a/data-raw/arbol_estadistico.xlsx
+++ b/data-raw/arbol_estadistico.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="121">
   <si>
     <t xml:space="preserve">Nivel1</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t xml:space="preserve">tool_0001_script_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tool_0001_script_002</t>
   </si>
   <si>
     <t xml:space="preserve">Anova 1 Way /n + /n Contrasts</t>
@@ -1258,7 +1261,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>58</v>
       </c>
@@ -1271,6 +1274,7 @@
       <c r="D22" s="7" t="s">
         <v>61</v>
       </c>
+      <c r="E22" s="7"/>
       <c r="F22" s="7" t="n">
         <v>25</v>
       </c>
@@ -1289,13 +1293,13 @@
         <v>60</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="24" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1309,13 +1313,13 @@
         <v>60</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="25" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1329,13 +1333,13 @@
         <v>60</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="26" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1349,13 +1353,13 @@
         <v>60</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1369,33 +1373,33 @@
         <v>60</v>
       </c>
       <c r="D27" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F27" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G27" s="4" t="s">
+    </row>
+    <row r="28" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="28" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="F28" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="29" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1406,16 +1410,16 @@
         <v>59</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="30" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1426,36 +1430,36 @@
         <v>59</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F30" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G30" s="4" t="s">
+    </row>
+    <row r="31" s="8" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="31" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="F31" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="32" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1466,16 +1470,16 @@
         <v>59</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D32" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="33" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1486,10 +1490,10 @@
         <v>59</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>25</v>
@@ -1498,24 +1502,24 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" s="11" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" s="9" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="35" s="11" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1526,16 +1530,16 @@
         <v>59</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D35" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="36" s="11" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1546,36 +1550,36 @@
         <v>59</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D36" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G36" s="4" t="s">
+    </row>
+    <row r="37" s="11" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="37" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" s="11" t="s">
+      <c r="F37" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="38" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1586,16 +1590,16 @@
         <v>59</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D38" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="39" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1606,16 +1610,16 @@
         <v>59</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D39" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="40" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1626,36 +1630,36 @@
         <v>59</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D40" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G40" s="4" t="s">
+    </row>
+    <row r="41" s="11" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="41" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" s="5" t="s">
+      <c r="F41" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="42" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1663,67 +1667,64 @@
         <v>58</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>60</v>
       </c>
       <c r="D42" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F42" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G42" s="4" t="s">
+    </row>
+    <row r="43" s="7" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="43" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="F43" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C43" s="6" t="s">
+    </row>
+    <row r="44" s="6" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
+      <c r="D44" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>59</v>
@@ -1735,18 +1736,18 @@
         <v>61</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>59</v>
@@ -1758,18 +1759,18 @@
         <v>61</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>59</v>
@@ -1781,30 +1782,30 @@
         <v>61</v>
       </c>
       <c r="E47" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F47" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G47" s="4" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>25</v>
@@ -1815,19 +1816,19 @@
     </row>
     <row r="49" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>25</v>
@@ -1838,19 +1839,19 @@
     </row>
     <row r="50" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>25</v>
@@ -1861,19 +1862,19 @@
     </row>
     <row r="51" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>25</v>
@@ -1882,7 +1883,29 @@
         <v>119</v>
       </c>
     </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
